--- a/results/TFL/tablas/tabla2_matriz_decisiones_binarias.xlsx
+++ b/results/TFL/tablas/tabla2_matriz_decisiones_binarias.xlsx
@@ -451,30 +451,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gemma-4-31B-it (Local)</t>
+          <t>Gemma-4-31B-it</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3078</v>
+        <v>2736</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>464 (15.07%)</t>
+          <t>470 (17.18%)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2612 (84.86%)</t>
+          <t>2259 (82.57%)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2 (0.06%)</t>
+          <t>7 (0.26%)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>112/114 (98.25%)</t>
+          <t>107/114 (93.86%)</t>
         </is>
       </c>
     </row>
@@ -485,56 +485,56 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3078</v>
+        <v>2736</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>463 (15.04%)</t>
+          <t>472 (17.25%)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2613 (84.89%)</t>
+          <t>2250 (82.24%)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2 (0.06%)</t>
+          <t>14 (0.51%)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>112/114 (98.25%)</t>
+          <t>102/114 (89.47%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gemini Flash 3.6 (Cloud)</t>
+          <t>Gemini Flash 3.7</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3078</v>
+        <v>2736</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>462 (15.01%)</t>
+          <t>465 (17.00%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2616 (84.99%)</t>
+          <t>2265 (82.79%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0 (0.00%)</t>
+          <t>6 (0.22%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>114/114 (100.00%)</t>
+          <t>108/114 (94.74%)</t>
         </is>
       </c>
     </row>
